--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>56.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,14 +1381,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>3</t>
@@ -1398,12 +1406,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1548,8 +1556,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1563,24 +1579,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -1588,7 +1604,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1598,12 +1614,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1612,7 +1628,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,37 +1642,37 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>2</t>
@@ -1674,12 +1690,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1701,27 +1717,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1731,101 +1747,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1839,12 +1863,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1888,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1912,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1926,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,7 +1997,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1987,12 +2007,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2002,72 +2022,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2120,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2115,24 +2143,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -2140,22 +2168,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2164,7 +2192,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.7</v>
+        <v>49</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2206,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,27 +2277,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2307,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2391,12 +2423,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2448,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2472,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.5</v>
+        <v>48.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2486,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,7 +2557,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2539,87 +2567,87 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2680,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2667,12 +2703,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2728,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2752,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.5</v>
+        <v>47.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,62 +2766,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2805,7 +2837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2820,12 +2852,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,67 +2867,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2960,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2948,7 +2988,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2968,12 +3008,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3032,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3046,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3056,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3029,14 +3069,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>6</t>
@@ -3054,12 +3094,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3204,8 +3244,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3224,7 +3272,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3292,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3316,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.1</v>
+        <v>42.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3330,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3340,10 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3305,14 +3353,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1</t>
@@ -3330,12 +3378,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -3480,8 +3528,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3520,12 +3576,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3600,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3614,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3624,10 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,14 +3637,14 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>4</t>
@@ -3606,12 +3662,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -3756,8 +3812,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3771,24 +3835,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -3796,22 +3860,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3884,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.1</v>
+        <v>32.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,40 +3898,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3882,17 +3946,17 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3909,7 +3973,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -3919,17 +3983,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,101 +4003,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4047,12 +4119,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4144,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4168,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4182,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q14" t="n">
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,12 +4253,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4200,12 +4268,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,67 +4283,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4308,8 +4376,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4323,12 +4399,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,12 +4424,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4372,7 +4448,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>29.3</v>
+        <v>32.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,65 +4462,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4461,12 +4533,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,7 +4548,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -4491,67 +4563,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4656,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4599,12 +4679,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4704,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4728,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>32.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,40 +4742,40 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4710,12 +4790,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -4737,12 +4817,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,7 +4832,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4767,67 +4847,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4940,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4875,24 +4963,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -4900,22 +4988,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4924,7 +5012,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>31.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +5026,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5013,27 +5097,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5127,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5151,12 +5243,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5268,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>26.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,40 +5306,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5262,12 +5354,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -5294,7 +5386,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5396,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,67 +5411,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5504,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5427,12 +5527,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5552,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,60 +5590,52 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -5565,12 +5657,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -5580,12 +5672,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5687,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5780,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6054,12 +6154,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6178,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>56.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6192,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6202,10 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6215,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6386,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6330,7 +6434,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6458,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6472,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6482,10 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6495,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6666,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6606,12 +6714,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6738,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6752,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6762,10 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,14 +6775,14 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>3</t>
@@ -6692,12 +6800,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -6842,8 +6950,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6857,24 +6973,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -6882,7 +6998,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6892,12 +7008,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -6906,7 +7022,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>48.3</v>
+        <v>49.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,37 +7036,37 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>36.6</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>34.3</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>65.2</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>2</t>
@@ -6968,12 +7084,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -6995,27 +7111,27 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7025,101 +7141,109 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7133,12 +7257,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,12 +7282,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7306,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>47.2</v>
+        <v>49</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7320,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>47.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,7 +7391,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -7281,12 +7401,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -7296,72 +7416,72 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>77.37</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -7394,8 +7514,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7409,24 +7537,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -7434,22 +7562,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7458,7 +7586,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>46.7</v>
+        <v>49</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7600,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>48.9</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S7" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,27 +7671,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7701,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7685,12 +7817,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7842,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7866,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>44.5</v>
+        <v>48.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7880,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>39.5</v>
+        <v>47.1</v>
       </c>
       <c r="Q8" t="n">
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T8" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>37.8</v>
+        <v>13.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,7 +7951,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -7833,87 +7961,87 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>77.37</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8074,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7961,12 +8097,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8122,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8146,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>43.5</v>
+        <v>47.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,62 +8160,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q9" t="n">
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8099,7 +8231,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -8114,12 +8246,12 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,67 +8261,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>36.44</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8354,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8242,7 +8382,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8262,12 +8402,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8426,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8440,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8450,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -8323,14 +8463,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>6</t>
@@ -8348,12 +8488,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -8498,8 +8638,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8518,7 +8666,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8686,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>40.1</v>
+        <v>42.7</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8724,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8734,10 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -8599,14 +8747,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1</t>
@@ -8624,12 +8772,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -8774,8 +8922,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8814,12 +8970,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8994,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +9008,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +9018,10 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,14 +9031,14 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>4</t>
@@ -8900,12 +9056,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -9050,8 +9206,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9065,24 +9229,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -9090,22 +9254,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9278,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.1</v>
+        <v>32.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,40 +9292,40 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>32.5</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>5.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9176,17 +9340,17 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -9203,7 +9367,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -9213,17 +9377,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,101 +9397,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9341,12 +9513,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9538,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9562,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30</v>
+        <v>32.7</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9576,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="Q14" t="n">
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>23.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,12 +9647,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -9494,12 +9662,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,67 +9677,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9602,8 +9770,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9617,12 +9793,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,12 +9818,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9666,7 +9842,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>29.3</v>
+        <v>32.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,65 +9856,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>17.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q15" t="n">
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T15" t="n">
         <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>22.4</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9755,12 +9927,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,7 +9942,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -9785,67 +9957,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +10050,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9893,12 +10073,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10098,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10122,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.6</v>
+        <v>32.2</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,40 +10136,40 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q16" t="n">
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>15.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10004,12 +10184,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -10031,12 +10211,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,7 +10226,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10061,67 +10241,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10334,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10169,24 +10357,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-24T00:00:00Z</t>
@@ -10194,22 +10382,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10218,7 +10406,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.5</v>
+        <v>31.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10420,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10307,27 +10491,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10521,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10445,12 +10637,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>670764</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Taylor Walls</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10662,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10686,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>28.1</v>
+        <v>26.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,40 +10700,40 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>5.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>18.6</v>
+        <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -10556,12 +10748,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -10588,7 +10780,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10790,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/20, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,67 +10805,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>86.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>95.5424</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0794</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.254</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>38.82</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0829</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10898,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10721,12 +10921,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>670764</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Taylor Walls</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10946,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10970,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,60 +10984,52 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>5.6</v>
+        <v>11.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>17.3</v>
+        <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -10859,12 +11051,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -10874,12 +11066,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11081,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>86.02</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>95.5424</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0794</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>68.28</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>38.82</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0829</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11174,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>

--- a/outputs/daily/hr_rankings_2026-10-23.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-23.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -1386,34 +1386,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1558,7 +1554,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -1628,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1652,7 +1648,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1670,34 +1666,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1842,7 +1834,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1936,7 +1928,7 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2122,7 +2114,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2192,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2216,7 +2208,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2402,7 +2394,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -2472,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2496,7 +2488,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -2682,7 +2674,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -2752,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2776,7 +2768,7 @@
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -2962,7 +2954,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -3032,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3056,7 +3048,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -3074,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3246,7 +3234,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -3316,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3340,7 +3328,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -3358,34 +3346,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3530,7 +3514,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -3600,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3624,7 +3608,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -3642,34 +3626,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3814,7 +3794,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -3884,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3908,7 +3888,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -3926,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4098,7 +4074,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -4168,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4192,7 +4168,7 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -4378,7 +4354,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -4448,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4472,7 +4448,7 @@
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -4658,7 +4634,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -4728,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4752,7 +4728,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>96.59999999999999</v>
@@ -4770,34 +4746,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4942,7 +4914,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -5012,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5036,7 +5008,7 @@
         <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -5222,7 +5194,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5316,7 +5288,7 @@
         <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5334,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5506,7 +5474,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5600,7 +5568,7 @@
         <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5616,28 +5584,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5782,7 +5754,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -6178,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.1</v>
+        <v>55.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6202,7 +6174,7 @@
         <v>34.3</v>
       </c>
       <c r="R2" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -6388,7 +6360,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -6458,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6482,7 +6454,7 @@
         <v>34.3</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
         <v>93.2</v>
@@ -6668,7 +6640,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -6738,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6762,7 +6734,7 @@
         <v>18.6</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
         <v>94.90000000000001</v>
@@ -6780,34 +6752,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6952,7 +6920,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -7022,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7046,7 +7014,7 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -7064,34 +7032,30 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7236,7 +7200,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -7306,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7330,7 +7294,7 @@
         <v>34.3</v>
       </c>
       <c r="R6" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -7516,7 +7480,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -7586,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7610,7 +7574,7 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -7796,7 +7760,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -7866,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7890,7 +7854,7 @@
         <v>34.3</v>
       </c>
       <c r="R8" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
         <v>76.2</v>
@@ -8076,7 +8040,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -8146,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>47.1</v>
+        <v>47</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8170,7 +8134,7 @@
         <v>34.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
         <v>94.90000000000001</v>
@@ -8356,7 +8320,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -8426,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>44</v>
+        <v>43.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8450,7 +8414,7 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
         <v>64.3</v>
@@ -8468,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8640,7 +8600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -8710,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8734,7 +8694,7 @@
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
         <v>93.2</v>
@@ -8752,34 +8712,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8924,7 +8880,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -8994,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9018,7 +8974,7 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
         <v>86.40000000000001</v>
@@ -9036,34 +8992,30 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9208,7 +9160,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -9278,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9302,7 +9254,7 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
         <v>76.2</v>
@@ -9320,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9492,7 +9440,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -9562,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9586,7 +9534,7 @@
         <v>34.3</v>
       </c>
       <c r="R14" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
         <v>44.8</v>
@@ -9772,7 +9720,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -9842,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9866,7 +9814,7 @@
         <v>34.3</v>
       </c>
       <c r="R15" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>64.3</v>
@@ -10052,7 +10000,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -10122,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10146,7 +10094,7 @@
         <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
         <v>96.59999999999999</v>
@@ -10164,34 +10112,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10336,7 +10280,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -10406,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10430,7 +10374,7 @@
         <v>34.3</v>
       </c>
       <c r="R17" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
         <v>52.4</v>
@@ -10616,7 +10560,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -10686,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10710,7 +10654,7 @@
         <v>17.3</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10728,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10900,7 +10840,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -10970,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10994,7 +10934,7 @@
         <v>18.6</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -11010,28 +10950,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11176,7 +11120,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
